--- a/DownloadedExcels/UserBulkUpload.xlsx
+++ b/DownloadedExcels/UserBulkUpload.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="dd/MM/yyyy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-MM-dd"/>
   </numFmts>
   <fonts count="1">
     <font>
